--- a/apiHirams/resources/templates/SITemplate.xlsx
+++ b/apiHirams/resources/templates/SITemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FAAECD-A0F6-45DB-A153-163169F4F5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4F464D-95E5-4C4B-A718-9FBE35132DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,7 +526,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -587,7 +587,11 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="235" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -597,12 +601,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="235" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="240">
@@ -1058,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:AA982"/>
+  <dimension ref="B1:AA999"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.88671875" style="17" customWidth="1"/>
@@ -1162,15 +1165,15 @@
     </row>
     <row r="4" spans="2:27" ht="20.25" customHeight="1">
       <c r="B4" s="3"/>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="26" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1192,7 +1195,7 @@
     </row>
     <row r="5" spans="2:27" ht="25.5" customHeight="1">
       <c r="B5" s="3"/>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="27" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="4"/>
@@ -1489,11 +1492,11 @@
       <c r="C15" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
       <c r="G15" s="24">
         <v>49293</v>
       </c>
@@ -1524,11 +1527,11 @@
     <row r="16" spans="2:27" ht="15" customHeight="1">
       <c r="B16" s="12"/>
       <c r="C16" s="13"/>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
       <c r="G16" s="14"/>
       <c r="H16" s="24"/>
       <c r="I16" s="2"/>
@@ -1552,9 +1555,9 @@
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="2:27" ht="17.25" customHeight="1">
-      <c r="D17" s="32"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="32"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
       <c r="G17" s="2"/>
       <c r="H17" s="24"/>
       <c r="I17" s="2"/>
@@ -1578,9 +1581,9 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D18" s="32"/>
+      <c r="D18" s="28"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="32"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
       <c r="I18" s="2"/>
@@ -28591,11 +28594,19 @@
       <c r="Z982" s="2"/>
       <c r="AA982" s="2"/>
     </row>
+    <row r="993" s="17" customFormat="1" ht="15" customHeight="1"/>
+    <row r="994" s="17" customFormat="1" ht="15" customHeight="1"/>
+    <row r="995" s="17" customFormat="1" ht="15" customHeight="1"/>
+    <row r="996" s="17" customFormat="1" ht="15" customHeight="1"/>
+    <row r="997" s="17" customFormat="1" ht="15" customHeight="1"/>
+    <row r="998" s="17" customFormat="1" ht="15" customHeight="1"/>
+    <row r="999" s="17" customFormat="1" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>

--- a/apiHirams/resources/templates/SITemplate.xlsx
+++ b/apiHirams/resources/templates/SITemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4F464D-95E5-4C4B-A718-9FBE35132DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F69C423-DE82-4949-B06E-F5FFADE71236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,18 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t xml:space="preserve">                DENR-PENRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                  000-535-043-028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                 Suqui, Calapan City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                Government</t>
-  </si>
-  <si>
     <t>Jo Anne Luisttro</t>
   </si>
   <si>
@@ -68,6 +56,18 @@
   <si>
     <t xml:space="preserve">Scan speed Up to 40 ppm </t>
   </si>
+  <si>
+    <t>DENR-PENRO</t>
+  </si>
+  <si>
+    <t>000-535-043-028</t>
+  </si>
+  <si>
+    <t>Suqui, Calapan City</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
 </sst>
 </file>
 
@@ -79,7 +79,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,13 +213,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -286,7 +279,7 @@
   </borders>
   <cellStyleXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -328,8 +321,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -520,7 +513,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -533,13 +526,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -553,13 +543,13 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="113" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="113" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -575,37 +565,42 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="235" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="235" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="240">
@@ -1064,19 +1059,19 @@
   <dimension ref="B1:AA999"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="17" customWidth="1"/>
-    <col min="4" max="4" width="11" style="17" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="17" customWidth="1"/>
-    <col min="6" max="6" width="23.33203125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="17" customWidth="1"/>
-    <col min="9" max="9" width="1.44140625" style="17" customWidth="1"/>
-    <col min="10" max="13" width="9.109375" style="17" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="17" customWidth="1"/>
-    <col min="15" max="27" width="8.6640625" style="17" customWidth="1"/>
-    <col min="28" max="16384" width="14.44140625" style="17"/>
+    <col min="1" max="1" width="3.88671875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="3.5546875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="11" style="16" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="1.44140625" style="16" customWidth="1"/>
+    <col min="10" max="13" width="9.109375" style="16" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="16" customWidth="1"/>
+    <col min="15" max="27" width="8.6640625" style="16" customWidth="1"/>
+    <col min="28" max="16384" width="14.44140625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:27" ht="26.25" customHeight="1">
@@ -1165,15 +1160,15 @@
     </row>
     <row r="4" spans="2:27" ht="20.25" customHeight="1">
       <c r="B4" s="3"/>
-      <c r="C4" s="26" t="s">
-        <v>0</v>
+      <c r="C4" s="31" t="s">
+        <v>6</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1195,15 +1190,15 @@
     </row>
     <row r="5" spans="2:27" ht="25.5" customHeight="1">
       <c r="B5" s="3"/>
-      <c r="C5" s="27" t="s">
-        <v>1</v>
+      <c r="C5" s="32" t="s">
+        <v>7</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -1225,15 +1220,15 @@
     </row>
     <row r="6" spans="2:27" ht="24" customHeight="1">
       <c r="B6" s="3"/>
-      <c r="C6" s="18" t="s">
-        <v>2</v>
+      <c r="C6" s="33" t="s">
+        <v>8</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1255,15 +1250,15 @@
     </row>
     <row r="7" spans="2:27" ht="27" customHeight="1">
       <c r="B7" s="3"/>
-      <c r="C7" s="18" t="s">
-        <v>3</v>
+      <c r="C7" s="33" t="s">
+        <v>9</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1340,10 +1335,10 @@
       <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="2:27" ht="14.25" customHeight="1">
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="9"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1368,17 +1363,17 @@
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="11" t="s">
-        <v>4</v>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="10" t="s">
+        <v>0</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>5</v>
+      <c r="F11" s="18" t="s">
+        <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>6</v>
+      <c r="G11" s="14" t="s">
+        <v>2</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="2"/>
@@ -1459,11 +1454,11 @@
     </row>
     <row r="14" spans="2:27" ht="18.75" customHeight="1">
       <c r="B14" s="3"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="1"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -1486,21 +1481,21 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B15" s="22">
+      <c r="B15" s="21">
         <v>1</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>7</v>
+      <c r="C15" s="22" t="s">
+        <v>3</v>
       </c>
-      <c r="D15" s="29" t="s">
-        <v>8</v>
+      <c r="D15" s="26" t="s">
+        <v>4</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="24">
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="23">
         <v>49293</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="23">
         <f>G15*B15</f>
         <v>49293</v>
       </c>
@@ -1525,15 +1520,15 @@
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="2:27" ht="15" customHeight="1">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="32" t="s">
-        <v>9</v>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="29" t="s">
+        <v>5</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="24"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="23"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1555,11 +1550,11 @@
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="2:27" ht="17.25" customHeight="1">
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="24"/>
+      <c r="H17" s="23"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1581,9 +1576,9 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D18" s="28"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="28"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="25"/>
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
       <c r="I18" s="2"/>
@@ -1608,7 +1603,7 @@
     </row>
     <row r="19" spans="2:27" ht="15" customHeight="1">
       <c r="G19" s="1"/>
-      <c r="H19" s="25"/>
+      <c r="H19" s="24"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1630,8 +1625,8 @@
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="2:27" ht="12.75" customHeight="1">
-      <c r="G20" s="10"/>
-      <c r="H20" s="20"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1653,13 +1648,13 @@
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="2:27" ht="15.75" customHeight="1">
-      <c r="B21" s="16"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="20">
+      <c r="B21" s="15"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="19">
         <f>H19/1.12</f>
         <v>0</v>
       </c>
@@ -1684,13 +1679,13 @@
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="2:27" ht="17.25" customHeight="1">
-      <c r="B22" s="16"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="20"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -1712,7 +1707,7 @@
       <c r="AA22" s="2"/>
     </row>
     <row r="23" spans="2:27" ht="4.5" customHeight="1">
-      <c r="B23" s="16"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1740,7 +1735,7 @@
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="2:27" ht="21" customHeight="1">
-      <c r="B24" s="16"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1774,7 +1769,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="20">
+      <c r="H25" s="19">
         <f>H20+H21</f>
         <v>0</v>
       </c>
@@ -1805,7 +1800,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="20"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1889,7 +1884,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="20"/>
+      <c r="H29" s="19"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -28594,19 +28589,23 @@
       <c r="Z982" s="2"/>
       <c r="AA982" s="2"/>
     </row>
-    <row r="993" s="17" customFormat="1" ht="15" customHeight="1"/>
-    <row r="994" s="17" customFormat="1" ht="15" customHeight="1"/>
-    <row r="995" s="17" customFormat="1" ht="15" customHeight="1"/>
-    <row r="996" s="17" customFormat="1" ht="15" customHeight="1"/>
-    <row r="997" s="17" customFormat="1" ht="15" customHeight="1"/>
-    <row r="998" s="17" customFormat="1" ht="15" customHeight="1"/>
-    <row r="999" s="17" customFormat="1" ht="15" customHeight="1"/>
+    <row r="993" s="16" customFormat="1" ht="15" customHeight="1"/>
+    <row r="994" s="16" customFormat="1" ht="15" customHeight="1"/>
+    <row r="995" s="16" customFormat="1" ht="15" customHeight="1"/>
+    <row r="996" s="16" customFormat="1" ht="15" customHeight="1"/>
+    <row r="997" s="16" customFormat="1" ht="15" customHeight="1"/>
+    <row r="998" s="16" customFormat="1" ht="15" customHeight="1"/>
+    <row r="999" s="16" customFormat="1" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
